--- a/Result/profitability/2641.xlsx
+++ b/Result/profitability/2641.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM58"/>
+  <dimension ref="A1:AM59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7800,6 +7800,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2641</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>571</v>
+      </c>
+      <c r="D59" t="n">
+        <v>343</v>
+      </c>
+      <c r="E59" t="n">
+        <v>228</v>
+      </c>
+      <c r="F59" t="n">
+        <v>39.94</v>
+      </c>
+      <c r="G59" t="n">
+        <v>196</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>34.41%</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>56</v>
+      </c>
+      <c r="J59" t="n">
+        <v>252</v>
+      </c>
+      <c r="K59" t="n">
+        <v>177</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="N59" t="n">
+        <v>41.9575</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
+      </c>
+      <c r="V59" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W59" t="n">
+        <v>-0.1699999999999999</v>
+      </c>
+      <c r="X59" t="n">
+        <v>-0.2394366197183098</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0.03000000000000114</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0.0007516913054372854</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>-0.09999999999999998</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>-0.15625</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>-2.219999999999999</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>-0.05265654648956353</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK59" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
